--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95988</v>
+        <v>95991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100104</v>
+        <v>100107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100368</v>
+        <v>100371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100368</v>
+        <v>100371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95991</v>
+        <v>95992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100107</v>
+        <v>100108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100371</v>
+        <v>100372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100371</v>
+        <v>100372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3338-2025 artfynd.xlsx
+++ b/artfynd/S 3338-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
         <v>136103735</v>
       </c>
       <c r="B8" t="n">
-        <v>95992</v>
+        <v>95997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136103719</v>
       </c>
       <c r="B17" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136103713</v>
       </c>
       <c r="B18" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136103760</v>
       </c>
       <c r="B20" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>136107235</v>
       </c>
       <c r="B21" t="n">
-        <v>100108</v>
+        <v>100113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>136103740</v>
       </c>
       <c r="B22" t="n">
-        <v>100372</v>
+        <v>100377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136107228</v>
       </c>
       <c r="B23" t="n">
-        <v>100372</v>
+        <v>100377</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136103729</v>
       </c>
       <c r="B26" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>136103710</v>
       </c>
       <c r="B27" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
